--- a/data/trans_camb/IP07B_R2-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP07B_R2-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-5.111445514468721</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.6517643278770392</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.875013903433674</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-2.838837021007618</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-3.541246290593656</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-1.228430071323864</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-9.647279458041625</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.840134195375001</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.857013983926173</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-7.595923985859756</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-6.749969656686397</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-4.92139612825526</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>-1.926981954406282</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.81047943717571</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.497943436391277</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0.4723095586895588</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>-1.13169708255164</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>4.218766110354828</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.9022955992227295</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.1150524021256123</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.4844919477216361</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.7335378554012523</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.7349182169862363</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2549372632193465</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.9141388711700886</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.944348008877221</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.8323060062473788</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>-0.2037404199614015</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>3.226902004702257</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1.719528267619948</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>5.343028124839557</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.2385200606180356</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.651400616325193</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-1.463538617894674</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.598775647941004</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.554987654938849</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-2.950626054620274</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-1.525557243950873</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-2.673096189785412</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-5.243385627916933</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.463370634903049</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.378439530707829</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-7.444932227547521</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-4.060179889052246</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-5.061555480001439</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>3.43121083521119</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9207287508492815</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.381187755418215</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-1.272512473765743</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1.297367620254286</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-0.4673119017829372</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.4092222070904311</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.7266475194984008</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.5270026178017213</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.4670784786862247</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.818419437656395</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,18 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-1</v>
+      </c>
       <c r="D14" s="6" t="inlineStr"/>
       <c r="E14" s="6" t="inlineStr"/>
       <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="n">
+        <v>-0.8934671924721047</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +884,18 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>4.702973831945304</v>
+      </c>
       <c r="D15" s="6" t="inlineStr"/>
       <c r="E15" s="6" t="inlineStr"/>
       <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="n">
+        <v>0.8258393458942485</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.5455505898693078</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +908,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-1.562780038688478</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1.508913203925393</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-2.602079991968874</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.07501385387243</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-2.06705897666333</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-1.346323950572565</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +934,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-5.169958596729317</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-5.288570073313611</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-9.239380616844775</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-5.262138365222148</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-5.722577528401261</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-4.145726362890954</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +960,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>2.233696372861504</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.146675142178818</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.323534070198856</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-0.03755070611479458</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1.491422114622418</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +986,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.6045490658872803</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.5837111079967654</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.4131363590628959</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.7972895765561308</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.5192933847451648</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -917,9 +1018,6 @@
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr"/>
       <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -934,9 +1032,6 @@
       <c r="F21" s="6" t="inlineStr"/>
       <c r="G21" s="6" t="inlineStr"/>
       <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1044,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>5.483683060980836</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.6442378490570944</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.09797658748609064</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>2.339502625983127</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.375328569718305</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1070,22 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="n">
+        <v>-8.013374410705813</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-7.907232311163398</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-1.929693960640287</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-4.577849703764296</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1094,22 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>14.14207761501423</v>
+      </c>
       <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="n">
+        <v>5.812659595070651</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>6.391546337909479</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>8.023958803058111</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>2.676554365696524</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1118,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
       <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="n">
+        <v>-0.1709124998695768</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.0259926105248964</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>1.145088245190117</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.1837075660848392</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1023,9 +1150,6 @@
       <c r="F26" s="6" t="inlineStr"/>
       <c r="G26" s="6" t="inlineStr"/>
       <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1040,9 +1164,6 @@
       <c r="F27" s="6" t="inlineStr"/>
       <c r="G27" s="6" t="inlineStr"/>
       <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1176,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-2.004383168296565</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-2.234334190140681</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-1.72701474885785</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-1.911980923121659</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-1.873649788815054</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-2.07284634956925</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1202,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-4.18234356862571</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-4.534281932955751</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-4.080058915937988</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-4.31219504949513</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-3.435688614327072</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-3.69313291320618</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1228,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>0.06517388171157686</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-0.04045231118922207</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.1400126362316983</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.360110269839624</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-0.5343638735156243</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-0.6860447514574948</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1254,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.5380366160074581</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.5997623736357316</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.5233048888315119</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.57935171954024</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.5321545082456375</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.588730368080901</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1280,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.8433230506134491</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.9104371152953726</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.8325976894121832</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.9180231752935284</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.7726819831771558</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.8299234654979362</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1306,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.1422787582401939</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.2034712796131044</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.1387709326489356</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.378246105886052</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>-0.1683869536382709</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>-0.1110101943642661</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1334,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
